--- a/annotations/task3_annotations.xlsx
+++ b/annotations/task3_annotations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Studies\UZH-M.Sc\THESIS\design-decisions-by-LLMs\annotations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F638F290-F846-4160-8503-EB8198A2B7E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D26C091-E490-45BC-8116-AA68C9895733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="360" windowWidth="25440" windowHeight="15270" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pypi-server" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2317" uniqueCount="620">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2317" uniqueCount="621">
   <si>
     <t>Step-level trajectory annotations — pypi-server</t>
   </si>
@@ -12614,6 +12614,9 @@
 - Arguments: {"command": "your_command_here"}
 If you want to end the task, please issue the following command: `echo COMPLETE_TASK_AND_SUBMIT_FINAL_OUTPUT`
 without any other command.</t>
+  </si>
+  <si>
+    <t>Harness</t>
   </si>
 </sst>
 </file>
@@ -13456,7 +13459,7 @@
   </autoFilter>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Model selection" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Harness selection" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Harness" dataDxfId="8"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Trial ID" dataDxfId="7"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Step" dataDxfId="6"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Thought" dataDxfId="5"/>
@@ -17666,8 +17669,8 @@
   <dimension ref="A1:J155"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="67" customWidth="1"/>
-    <col min="2" max="2" width="56.296875" customWidth="1"/>
+    <col min="1" max="1" width="44.5" customWidth="1"/>
+    <col min="2" max="2" width="33.3984375" customWidth="1"/>
     <col min="3" max="3" width="38" customWidth="1"/>
     <col min="4" max="4" width="13.296875" customWidth="1"/>
     <col min="5" max="5" width="66.5" customWidth="1"/>
@@ -17724,7 +17727,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>4</v>
+        <v>620</v>
       </c>
       <c r="C5" s="34" t="s">
         <v>5</v>
